--- a/ingest/2026-09-03/grandeur_ls_upload_2026-09-03.xlsx
+++ b/ingest/2026-09-03/grandeur_ls_upload_2026-09-03.xlsx
@@ -8876,24 +8876,29 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>3f1ed949-8615-4feb-b12c-ec27fcec7287</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>GRND7ATLANTIC8936</t>
+          <t>GRND7ATLANTICGF8936</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>GRNDLVP-0002</t>
+          <t>SPC-GRAN-0001</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>GRNDLVP-SPC - Atlantic (8936) Click | 7" x 5mm x RL - 26.72sf/b</t>
+          <t>GRNDLVP-SPC - Atlantic (GF8936) Click | 7" x 5mm x RL - 26.72sf/b</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Supplier SKU: 8936 | Wear layer (mil): 12 | Install method: Float | Underpad included: TRUE | IIC rating: 72 | STC rating: 70 | MAP price ($/sf): 4.29 | Promo cost ($/sf): 1.59 | Promo end date: 2026-09-30 | Last price update: 2026-09-01 | Price last changed by: Cowork | Active: TRUE | Waterproof: TRUE | Salesperson notes: AMBIGUOUS MATCH — could not be reconciled against the live catalogue with confidence; SKU below is the run-generated placeholder, NOT a real catalogue SKU. Colour placeholder "8936" vs live "GF8936" (SPC-GRAN-0001, Supplier SKU GF8936). Partial supplier-code match only — not confident enough to adopt. Confirm with Grandeur, then either adopt SPC-GRAN-0001 or keep as new. Resolve before import. | Colour name not provided by supplier -- product identified only by code '8936'. Used as colour placeholder; confirm actual colour name with Grandeur. SALE item, no regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 4.0mm SPC + 1mm underpad (material not named). *Two-side Closed Treads Available. | MatchStatus: ambiguous</t>
+          <t>Supplier SKU: GF8936 | Wear layer (mil): 12 | Install method: Float | Underpad included: TRUE | IIC rating: 72 | STC rating: 70 | MAP price ($/sf): 4.29 | Promo cost ($/sf): 1.59 | Promo end date: 2026-09-30 | Last price update: 2026-09-01 | Price last changed by: Cowork | Active: TRUE | Waterproof: TRUE | Salesperson notes: Resolved 2026-09-03 (Albert): adopted live SPC-GRAN-0001 — price-list code "8936" confirmed as the same product as live "GF8936". SKU, LS handle, Lightspeed ID and Supplier SKU taken from the live record per RULE 0. | Colour name not provided by supplier -- product identified only by code '8936'. Used as colour placeholder; confirm actual colour name with Grandeur. SALE item, no regular equivalent in this collection -&gt; Cost/unit=SALE price per Sale rule 3. Composition: 4.0mm SPC + 1mm underpad (material not named). *Two-side Closed Treads Available. | MatchStatus: matched</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
